--- a/version2.xlsx
+++ b/version2.xlsx
@@ -946,7 +946,7 @@
           <t>비 고</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>crawlable</t>
         </is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="F3" s="33" t="n"/>
-      <c r="G3" t="b">
+      <c r="G3" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="F4" s="34" t="n"/>
-      <c r="G4" t="b">
+      <c r="G4" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="F5" s="34" t="n"/>
-      <c r="G5" t="b">
+      <c r="G5" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="F6" s="34" t="n"/>
-      <c r="G6" t="b">
+      <c r="G6" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F7" s="34" t="n"/>
-      <c r="G7" t="b">
+      <c r="G7" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="F8" s="34" t="n"/>
-      <c r="G8" t="b">
+      <c r="G8" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="F9" s="34" t="n"/>
-      <c r="G9" t="b">
+      <c r="G9" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="F10" s="34" t="n"/>
-      <c r="G10" t="b">
+      <c r="G10" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="F11" s="34" t="n"/>
-      <c r="G11" t="b">
+      <c r="G11" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="F12" s="34" t="n"/>
-      <c r="G12" t="b">
+      <c r="G12" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="F13" s="34" t="n"/>
-      <c r="G13" t="b">
+      <c r="G13" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="F14" s="34" t="n"/>
-      <c r="G14" t="b">
+      <c r="G14" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="F15" s="34" t="n"/>
-      <c r="G15" t="b">
+      <c r="G15" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="F16" s="34" t="n"/>
-      <c r="G16" t="b">
+      <c r="G16" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="F17" s="34" t="n"/>
-      <c r="G17" t="b">
+      <c r="G17" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="F18" s="34" t="n"/>
-      <c r="G18" t="b">
+      <c r="G18" s="0" t="b">
         <v>0</v>
       </c>
       <c r="K18" s="44" t="inlineStr">
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="F19" s="34" t="n"/>
-      <c r="G19" t="b">
+      <c r="G19" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="F20" s="34" t="n"/>
-      <c r="G20" t="b">
+      <c r="G20" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="F21" s="34" t="n"/>
-      <c r="G21" t="b">
+      <c r="G21" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="F22" s="34" t="n"/>
-      <c r="G22" t="b">
+      <c r="G22" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
         </is>
       </c>
       <c r="F23" s="34" t="n"/>
-      <c r="G23" t="b">
+      <c r="G23" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="F24" s="34" t="n"/>
-      <c r="G24" t="b">
+      <c r="G24" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="F25" s="34" t="n"/>
-      <c r="G25" t="b">
+      <c r="G25" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="F26" s="34" t="n"/>
-      <c r="G26" t="b">
+      <c r="G26" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c r="F27" s="34" t="n"/>
-      <c r="G27" t="b">
+      <c r="G27" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F28" s="34" t="n"/>
-      <c r="G28" t="b">
+      <c r="G28" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="F29" s="34" t="n"/>
-      <c r="G29" t="b">
+      <c r="G29" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="F30" s="34" t="n"/>
-      <c r="G30" t="b">
+      <c r="G30" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" s="35" t="n"/>
-      <c r="G31" t="b">
+      <c r="G31" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="F32" s="35" t="n"/>
-      <c r="G32" t="b">
+      <c r="G32" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="F33" s="35" t="n"/>
-      <c r="G33" t="b">
+      <c r="G33" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="F34" s="35" t="n"/>
-      <c r="G34" t="b">
+      <c r="G34" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="F35" s="35" t="n"/>
-      <c r="G35" t="b">
+      <c r="G35" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="F36" s="35" t="n"/>
-      <c r="G36" t="b">
+      <c r="G36" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="F37" s="35" t="n"/>
-      <c r="G37" t="b">
+      <c r="G37" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F38" s="35" t="n"/>
-      <c r="G38" t="b">
+      <c r="G38" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="F39" s="35" t="n"/>
-      <c r="G39" t="b">
+      <c r="G39" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="F40" s="35" t="n"/>
-      <c r="G40" t="b">
+      <c r="G40" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="F41" s="35" t="n"/>
-      <c r="G41" t="b">
+      <c r="G41" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="F42" s="35" t="n"/>
-      <c r="G42" t="b">
+      <c r="G42" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="F43" s="35" t="n"/>
-      <c r="G43" t="b">
+      <c r="G43" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="F44" s="35" t="n"/>
-      <c r="G44" t="b">
+      <c r="G44" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="F45" s="35" t="n"/>
-      <c r="G45" t="b">
+      <c r="G45" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="F46" s="35" t="n"/>
-      <c r="G46" t="b">
+      <c r="G46" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="F47" s="35" t="n"/>
-      <c r="G47" t="b">
+      <c r="G47" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
         </is>
       </c>
       <c r="F48" s="35" t="n"/>
-      <c r="G48" t="b">
+      <c r="G48" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="F49" s="35" t="n"/>
-      <c r="G49" t="b">
+      <c r="G49" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="F50" s="35" t="n"/>
-      <c r="G50" t="b">
+      <c r="G50" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="F51" s="35" t="n"/>
-      <c r="G51" t="b">
+      <c r="G51" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="F52" s="35" t="n"/>
-      <c r="G52" t="b">
+      <c r="G52" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="F53" s="35" t="n"/>
-      <c r="G53" t="b">
+      <c r="G53" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="F54" s="35" t="n"/>
-      <c r="G54" t="b">
+      <c r="G54" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="F55" s="35" t="n"/>
-      <c r="G55" t="b">
+      <c r="G55" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="F56" s="35" t="n"/>
-      <c r="G56" t="b">
+      <c r="G56" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
         </is>
       </c>
       <c r="F57" s="35" t="n"/>
-      <c r="G57" t="b">
+      <c r="G57" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F58" s="35" t="n"/>
-      <c r="G58" t="b">
+      <c r="G58" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="F59" s="35" t="n"/>
-      <c r="G59" t="b">
+      <c r="G59" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="F60" s="35" t="n"/>
-      <c r="G60" t="b">
+      <c r="G60" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="F61" s="35" t="n"/>
-      <c r="G61" t="b">
+      <c r="G61" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="F62" s="35" t="n"/>
-      <c r="G62" t="b">
+      <c r="G62" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="F63" s="35" t="n"/>
-      <c r="G63" t="b">
+      <c r="G63" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="F64" s="35" t="n"/>
-      <c r="G64" t="b">
+      <c r="G64" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="F65" s="35" t="n"/>
-      <c r="G65" t="b">
+      <c r="G65" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="F66" s="35" t="n"/>
-      <c r="G66" t="b">
+      <c r="G66" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
         </is>
       </c>
       <c r="F67" s="35" t="n"/>
-      <c r="G67" t="b">
+      <c r="G67" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="F68" s="35" t="n"/>
-      <c r="G68" t="b">
+      <c r="G68" s="0" t="b">
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n"/>
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="F69" s="36" t="n"/>
-      <c r="G69" t="b">
+      <c r="G69" s="0" t="b">
         <v>0</v>
       </c>
       <c r="H69" s="28" t="n"/>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="F70" s="40" t="n"/>
-      <c r="G70" t="b">
+      <c r="G70" s="0" t="b">
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n"/>
@@ -2862,7 +2862,7 @@
           <t>비 고</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>crawlable</t>
         </is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="F3" s="56" t="n"/>
-      <c r="G3" t="b">
+      <c r="G3" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="F4" s="57" t="n"/>
-      <c r="G4" t="b">
+      <c r="G4" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="F5" s="57" t="n"/>
-      <c r="G5" t="b">
+      <c r="G5" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="F6" s="57" t="n"/>
-      <c r="G6" t="b">
+      <c r="G6" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="F7" s="57" t="n"/>
-      <c r="G7" t="b">
+      <c r="G7" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="F8" s="57" t="n"/>
-      <c r="G8" t="b">
+      <c r="G8" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="F9" s="57" t="n"/>
-      <c r="G9" t="b">
+      <c r="G9" s="0" t="b">
         <v>0</v>
       </c>
       <c r="J9" s="45" t="n"/>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="F10" s="57" t="n"/>
-      <c r="G10" t="b">
+      <c r="G10" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="F11" s="57" t="n"/>
-      <c r="G11" t="b">
+      <c r="G11" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="F12" s="57" t="n"/>
-      <c r="G12" t="b">
+      <c r="G12" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="F13" s="57" t="n"/>
-      <c r="G13" t="b">
+      <c r="G13" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="F14" s="57" t="n"/>
-      <c r="G14" t="b">
+      <c r="G14" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="F15" s="57" t="n"/>
-      <c r="G15" t="b">
+      <c r="G15" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         </is>
       </c>
       <c r="F16" s="57" t="n"/>
-      <c r="G16" t="b">
+      <c r="G16" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="F17" s="57" t="n"/>
-      <c r="G17" t="b">
+      <c r="G17" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
         </is>
       </c>
       <c r="F18" s="57" t="n"/>
-      <c r="G18" t="b">
+      <c r="G18" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="F19" s="57" t="n"/>
-      <c r="G19" t="b">
+      <c r="G19" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="F20" s="57" t="n"/>
-      <c r="G20" t="b">
+      <c r="G20" s="0" t="b">
         <v>0</v>
       </c>
       <c r="K20" s="44" t="inlineStr">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="F21" s="57" t="n"/>
-      <c r="G21" t="b">
+      <c r="G21" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="F22" s="58" t="n"/>
-      <c r="G22" t="b">
+      <c r="G22" s="0" t="b">
         <v>0</v>
       </c>
     </row>
